--- a/Store_Inventory_Tracker.xlsx
+++ b/Store_Inventory_Tracker.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,7 +39,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="22"/>
+      <sz val="21"/>
     </font>
     <font>
       <i val="1"/>
@@ -49,25 +49,20 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="00375623"/>
       <sz val="16"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="009C6500"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -76,22 +71,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="00217346"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F6FC"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,39 +97,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -231,9 +228,8 @@
       </tx>
     </title>
     <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
+      <doughnutChart>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -258,33 +254,13 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
+        <firstSliceAng val="0"/>
+        <holeSize val="55"/>
+      </doughnutChart>
     </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -382,63 +358,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Stock Value by Supplier</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Calc'!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Calc'!$D$2:$D$6</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Calc'!$E$2:$E$6</f>
-            </numRef>
-          </val>
-        </ser>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Units in Stock by Category</a:t>
             </a:r>
           </a:p>
@@ -500,6 +419,63 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Stock Value by Supplier</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Calc'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Calc'!$D$2:$D$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Calc'!$E$2:$E$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -885,11 +861,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="00217346"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -910,7 +886,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RETAIL STORE - INVENTORY OVERVIEW</t>
+          <t>📦  RETAIL STORE — STOCK CONTROL HUB</t>
         </is>
       </c>
     </row>
@@ -918,110 +894,70 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Live formulas - replace Data with your stock export and everything updates</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="3" t="inlineStr">
+          <t>Live inventory view · low-stock rows are flagged automatically in the Data sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>TOTAL STOCK VALUE</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL SKUs</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>SKUs TRACKED</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>UNITS IN STOCK</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>LOW-STOCK ITEMS</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>UNITS IN STOCK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="4">
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="4">
         <f>SUM(Data!H2:H31)</f>
         <v/>
       </c>
-      <c r="E5" s="5">
+      <c r="E6" s="5">
         <f>COUNTA(Data!A2:A31)</f>
         <v/>
       </c>
-      <c r="H5" s="5">
+      <c r="H6" s="5">
+        <f>SUM(Data!E2:E31)</f>
+        <v/>
+      </c>
+      <c r="K6" s="5">
         <f>SUMPRODUCT(--(Data!E2:E31&lt;Data!F2:F31))</f>
         <v/>
       </c>
-      <c r="K5" s="5">
-        <f>SUM(Data!E2:E31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>TOP CATEGORY</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>HIGHEST-VALUE ITEM</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>AVG ITEM VALUE</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>MAIN SUPPLIER</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="B8" s="7">
-        <f>INDEX(Calc!A2:A6,MATCH(MAX(Calc!B2:B6),Calc!B2:B6,0))</f>
-        <v/>
-      </c>
-      <c r="E8" s="7">
-        <f>INDEX(Data!C2:C31,MATCH(MAX(Data!H2:H31),Data!H2:H31,0))</f>
-        <v/>
-      </c>
-      <c r="H8" s="7">
-        <f>AVERAGE(Data!H2:H31)</f>
-        <v/>
-      </c>
-      <c r="K8" s="7">
-        <f>INDEX(Calc!D2:D6,MATCH(MAX(Calc!E2:E6),Calc!E2:E6,0))</f>
-        <v/>
-      </c>
-    </row>
+    </row>
+    <row r="8">
+      <c r="B8" s="6">
+        <f>"⚠  LOW-STOCK ALERT: "&amp;SUMPRODUCT(--(Data!E2:E31&lt;Data!F2:F31))&amp;" items are below reorder point — open the Data sheet to see them highlighted in red"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9"/>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="H4:I4"/>
+  <mergeCells count="11">
     <mergeCell ref="K5:L5"/>
-    <mergeCell ref="H7:I7"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A1:N2"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A3:N3"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="B8:L9"/>
+    <mergeCell ref="H6:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1031,6 +967,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00217346"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1048,78 +985,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Stock Qty</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Reorder Point</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Stock Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SKU-5433</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Cookware Set</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>EuroParts Trading</t>
         </is>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" t="n">
         <v>115</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" t="n">
         <v>20</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="8" t="n">
         <v>76.84999999999999</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="8">
         <f>E2*G2</f>
         <v/>
       </c>
@@ -1151,45 +1088,45 @@
       <c r="F3" t="n">
         <v>30</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" s="8" t="n">
         <v>43.88</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="8">
         <f>E3*G3</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>SKU-1110</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Sneakers</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>NordSupply</t>
         </is>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" t="n">
         <v>122</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" t="n">
         <v>25</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="8" t="n">
         <v>47.57</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <f>E4*G4</f>
         <v/>
       </c>
@@ -1221,45 +1158,45 @@
       <c r="F5" t="n">
         <v>25</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="8" t="n">
         <v>61.57</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="8">
         <f>E5*G5</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>SKU-3934</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Power Bank</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>MegaImport</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" t="n">
         <v>180</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" t="n">
         <v>40</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="8" t="n">
         <v>28.54</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <f>E6*G6</f>
         <v/>
       </c>
@@ -1291,45 +1228,45 @@
       <c r="F7" t="n">
         <v>50</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="8" t="n">
         <v>29.42</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="8">
         <f>E7*G7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>SKU-7708</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Kettle</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>GlobalWholesale</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" t="n">
         <v>174</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" t="n">
         <v>25</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="8" t="n">
         <v>26.46</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="8">
         <f>E8*G8</f>
         <v/>
       </c>
@@ -1361,45 +1298,45 @@
       <c r="F9" t="n">
         <v>20</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="8" t="n">
         <v>29.81</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="8">
         <f>E9*G9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>SKU-4018</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Wireless Mouse</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>NordSupply</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" t="n">
         <v>171</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" t="n">
         <v>30</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="8" t="n">
         <v>21.17</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <f>E10*G10</f>
         <v/>
       </c>
@@ -1431,45 +1368,45 @@
       <c r="F11" t="n">
         <v>20</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="8" t="n">
         <v>20.42</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="8">
         <f>E11*G11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>SKU-5527</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Plush Bear</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>NordSupply</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" t="n">
         <v>153</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" t="n">
         <v>40</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="8" t="n">
         <v>20.95</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="8">
         <f>E12*G12</f>
         <v/>
       </c>
@@ -1501,45 +1438,45 @@
       <c r="F13" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="8" t="n">
         <v>29.32</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="8">
         <f>E13*G13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>SKU-2305</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Bluetooth Speaker</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>EuroParts Trading</t>
         </is>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" t="n">
         <v>73</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" t="n">
         <v>20</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="8" t="n">
         <v>38.19</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="8">
         <f>E14*G14</f>
         <v/>
       </c>
@@ -1571,45 +1508,45 @@
       <c r="F15" t="n">
         <v>30</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="8" t="n">
         <v>23.42</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="8">
         <f>E15*G15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>SKU-1528</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Knife Set</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>GlobalWholesale</t>
         </is>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" t="n">
         <v>69</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" t="n">
         <v>50</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="8" t="n">
         <v>35.7</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="8">
         <f>E16*G16</f>
         <v/>
       </c>
@@ -1641,45 +1578,45 @@
       <c r="F17" t="n">
         <v>50</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="8" t="n">
         <v>56.91</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="8">
         <f>E17*G17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>SKU-9192</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Sports</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Resistance Bands</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>VestDistribution</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" t="n">
         <v>167</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" t="n">
         <v>20</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="8">
         <f>E18*G18</f>
         <v/>
       </c>
@@ -1711,45 +1648,45 @@
       <c r="F19" t="n">
         <v>20</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="8" t="n">
         <v>21.95</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="8">
         <f>E19*G19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>SKU-7598</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Toys</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>RC Car</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>VestDistribution</t>
         </is>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" t="n">
         <v>35</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" t="n">
         <v>50</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="8" t="n">
         <v>52.84</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="8">
         <f>E20*G20</f>
         <v/>
       </c>
@@ -1781,45 +1718,45 @@
       <c r="F21" t="n">
         <v>50</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="8" t="n">
         <v>18.26</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H21" s="8">
         <f>E21*G21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>SKU-7599</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Jeans</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>NordSupply</t>
         </is>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" t="n">
         <v>55</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" t="n">
         <v>50</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="8" t="n">
         <v>32.86</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="8">
         <f>E22*G22</f>
         <v/>
       </c>
@@ -1851,45 +1788,45 @@
       <c r="F23" t="n">
         <v>25</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G23" s="8" t="n">
         <v>11.92</v>
       </c>
-      <c r="H23" s="11">
+      <c r="H23" s="8">
         <f>E23*G23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>SKU-7123</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Storage Box</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>GlobalWholesale</t>
         </is>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" t="n">
         <v>154</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" t="n">
         <v>20</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="8" t="n">
         <v>10.49</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="8">
         <f>E24*G24</f>
         <v/>
       </c>
@@ -1921,45 +1858,45 @@
       <c r="F25" t="n">
         <v>20</v>
       </c>
-      <c r="G25" s="11" t="n">
+      <c r="G25" s="8" t="n">
         <v>10.38</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="8">
         <f>E25*G25</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>SKU-9898</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Clothing</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>T-Shirt Basic</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>MegaImport</t>
         </is>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" t="n">
         <v>115</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" t="n">
         <v>50</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="8" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="8">
         <f>E26*G26</f>
         <v/>
       </c>
@@ -1991,45 +1928,45 @@
       <c r="F27" t="n">
         <v>20</v>
       </c>
-      <c r="G27" s="11" t="n">
+      <c r="G27" s="8" t="n">
         <v>14.11</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="8">
         <f>E27*G27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>SKU-7906</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Phone Case</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>EuroParts Trading</t>
         </is>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" t="n">
         <v>51</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" t="n">
         <v>20</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="8" t="n">
         <v>9.91</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="8">
         <f>E28*G28</f>
         <v/>
       </c>
@@ -2061,45 +1998,45 @@
       <c r="F29" t="n">
         <v>30</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="G29" s="8" t="n">
         <v>17.73</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="8">
         <f>E29*G29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>SKU-3299</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>USB-C Cable</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>EuroParts Trading</t>
         </is>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" t="n">
         <v>11</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" t="n">
         <v>50</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="8" t="n">
         <v>11.99</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="8">
         <f>E30*G30</f>
         <v/>
       </c>
@@ -2131,16 +2068,30 @@
       <c r="F31" t="n">
         <v>50</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G31" s="8" t="n">
         <v>11.32</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="8">
         <f>E31*G31</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H31"/>
+  <conditionalFormatting sqref="A2:H31">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E2&lt;$F2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H31">
+    <cfRule type="dataBar" priority="2">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="00217346"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2192,7 +2143,7 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Items in Stock</t>
+          <t>Units</t>
         </is>
       </c>
     </row>
